--- a/clustering logboek.xlsx
+++ b/clustering logboek.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serza\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serza\Documents\GitHub\DEAI-Serzat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A824972-8539-4D47-B0F4-00328B035BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C56B73-DF2F-4D47-B61D-9359409AE518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="2310" windowWidth="28800" windowHeight="14970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,61 +25,212 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
-  <si>
-    <t>Experiment</t>
-  </si>
-  <si>
-    <t>Gebruikte Features</t>
-  </si>
-  <si>
-    <t>Aantal Clusters (k)</t>
-  </si>
-  <si>
-    <t>Hyperparameters</t>
-  </si>
-  <si>
-    <t>Evaluatiemetriek (Silhouette Score)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>Initiële Run</t>
   </si>
   <si>
-    <t>Gr Liv Area, Year Built, Neighborhood</t>
-  </si>
-  <si>
-    <t>n_init=10</t>
-  </si>
-  <si>
-    <t>0.1171</t>
-  </si>
-  <si>
-    <t>Experiment 1</t>
-  </si>
-  <si>
-    <t>Gr Liv Area, Year Built, Neighborhood, Overall Qual, Garage</t>
-  </si>
-  <si>
-    <t>init='random', n_init=20, max_iter=500</t>
-  </si>
-  <si>
-    <t>0.1279</t>
-  </si>
-  <si>
-    <t>Experiment 2</t>
-  </si>
-  <si>
-    <t>Gr Liv Area, Overall Qual, House Style</t>
-  </si>
-  <si>
-    <t>0.3813</t>
+    <t>Exp #</t>
+  </si>
+  <si>
+    <t>Algoritme &amp; Instellingen</t>
+  </si>
+  <si>
+    <t>Silhouette Score</t>
+  </si>
+  <si>
+    <t>Brede set (5 features)</t>
+  </si>
+  <si>
+    <t>KMeans (K=3) + StandardScaler</t>
+  </si>
+  <si>
+    <t>~0.11</t>
+  </si>
+  <si>
+    <t>Meerdere dimensies en ruis maken de scheiding onduidelijk.</t>
+  </si>
+  <si>
+    <t>Meer Clusters</t>
+  </si>
+  <si>
+    <t>KMeans (K=5) + StandardScaler</t>
+  </si>
+  <si>
+    <t>~0.10</t>
+  </si>
+  <si>
+    <t>Meer clusters toevoegen lost het probleem van de vele dimensies niet op.</t>
+  </si>
+  <si>
+    <t>Feature Reductie</t>
+  </si>
+  <si>
+    <t>Alleen Oppervlakte &amp; Prijs</t>
+  </si>
+  <si>
+    <t>~0.35</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">De </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Curse of Dimensionality</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> doorbroken. Score stijgt enorm.</t>
+    </r>
+  </si>
+  <si>
+    <t>Clusters testen</t>
+  </si>
+  <si>
+    <t>~0.36</t>
+  </si>
+  <si>
+    <t>K=5 geeft een redelijke score, maar is lastig te interpreteren.</t>
+  </si>
+  <si>
+    <t>Elbow Method</t>
+  </si>
+  <si>
+    <t>Zoeken naar optimale K</t>
+  </si>
+  <si>
+    <t>KMeans (K=1 t/m 10)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Wiskundig bewijs geleverd via grafiek dat de ideale splitsing bij </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>K=2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ligt.</t>
+    </r>
+  </si>
+  <si>
+    <t>Optimale K Toepassen</t>
+  </si>
+  <si>
+    <t>KMeans (K=2) + StandardScaler</t>
+  </si>
+  <si>
+    <t>~0.38</t>
+  </si>
+  <si>
+    <r>
+      <t>Toppunt van stabiliteit.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> De meest logische scheiding van de data.</t>
+    </r>
+  </si>
+  <si>
+    <t>Alternatieve Scaler</t>
+  </si>
+  <si>
+    <t>KMeans (K=2) + MinMaxScaler</t>
+  </si>
+  <si>
+    <t>MinMaxScaler presteert vrijwel identiek aan StandardScaler.</t>
+  </si>
+  <si>
+    <t>Log-Transformatie</t>
+  </si>
+  <si>
+    <t>Log(SalePrice) &amp; Oppervlakte</t>
+  </si>
+  <si>
+    <t>Het transformeren van uitschieters (zeer dure huizen) gaf hier geen voordeel.</t>
+  </si>
+  <si>
+    <t>PCA (Dimensiereductie)</t>
+  </si>
+  <si>
+    <t>5 features samengedrukt naar 2</t>
+  </si>
+  <si>
+    <t>PCA + KMeans (K=3)</t>
+  </si>
+  <si>
+    <t>~0.40</t>
+  </si>
+  <si>
+    <t>Zeer geavanceerde methode. Goede score, maar clusters zijn moeilijker uit te leggen.</t>
+  </si>
+  <si>
+    <t>Finaal Model &amp; Analyse</t>
+  </si>
+  <si>
+    <t>KMeans (K=2) + Inverse Transform</t>
+  </si>
+  <si>
+    <r>
+      <t>Beste Business Value.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Duidelijke scheiding tussen 'Standaard' en 'Luxe' huizen.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Conclusie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doel / Features </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omschrijving </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,13 +251,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -136,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -146,6 +310,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -435,74 +611,227 @@
     <col min="3" max="3" width="29.5703125" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.5703125" customWidth="1"/>
+    <col min="6" max="6" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="78.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="78" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="C2" s="3">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="126" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="101.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
-        <v>5</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
+      <c r="D11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
